--- a/artfynd/Norrnäs artfynd.xlsx
+++ b/artfynd/Norrnäs artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96203024</v>
+        <v>17226080</v>
       </c>
       <c r="B2" t="n">
-        <v>80083</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>norrnäs, Ång</t>
+          <t>Mellan Bjurvik och Norrnäs, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>695021</v>
+        <v>694554</v>
       </c>
       <c r="R2" t="n">
-        <v>7085824</v>
+        <v>7086408</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-06-06</t>
+          <t>2013-06-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-06-06</t>
+          <t>2013-06-16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -757,19 +754,36 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AN2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Magnus Johansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Magnus Johansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -780,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>74543224</v>
+        <v>17226079</v>
       </c>
       <c r="B3" t="n">
-        <v>91263</v>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -791,37 +805,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Vikströms-Gravabergsmyran, Ång</t>
+          <t>Mellan Bjurvik och Norrnäs, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>694997</v>
+        <v>694448</v>
       </c>
       <c r="R3" t="n">
-        <v>7086245</v>
+        <v>7086492</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -845,12 +859,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2018-11-01</t>
+          <t>2013-06-16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2018-11-01</t>
+          <t>2013-06-16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -861,26 +875,48 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AN3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Salix caprea</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anna Hallmén</t>
+          <t>Magnus Johansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anna Hallmén</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Magnus Johansson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>17226079</v>
+        <v>74543072</v>
       </c>
       <c r="B4" t="n">
-        <v>80083</v>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,17 +944,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mellan Bjurvik och Norrnäs, Ång</t>
+          <t>Vikströms-Gravabergsmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>694448</v>
+        <v>694532</v>
       </c>
       <c r="R4" t="n">
-        <v>7086492</v>
+        <v>7086592</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -942,12 +978,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2013-06-16</t>
+          <t>2018-11-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2013-06-16</t>
+          <t>2018-11-01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -958,48 +994,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AN4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>1 substratenheter # Salix caprea</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Magnus Johansson</t>
+          <t>Anna Hallmén</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Johansson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Anna Hallmén</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>17226078</v>
+        <v>17226040</v>
       </c>
       <c r="B5" t="n">
-        <v>91263</v>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,34 +1021,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mellan Bjurvik och Norrnäs, Ång</t>
+          <t>600 m VNV om sjön Bjärtens nordvästspets, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>694454</v>
+        <v>695091</v>
       </c>
       <c r="R5" t="n">
-        <v>7086467</v>
+        <v>7086228</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,12 +1075,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2013-06-16</t>
+          <t>2013-05-30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2013-06-16</t>
+          <t>2013-05-30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1089,11 +1103,11 @@
         </is>
       </c>
       <c r="AN5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>1 substratenheter # Picea abies</t>
+          <t>2 substratenheter # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1115,10 +1129,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>17226040</v>
+        <v>96203024</v>
       </c>
       <c r="B6" t="n">
-        <v>82792</v>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1126,34 +1140,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>600 m VNV om sjön Bjärtens nordvästspets, Ång</t>
+          <t>norrnäs, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>695091</v>
+        <v>695021</v>
       </c>
       <c r="R6" t="n">
-        <v>7086228</v>
+        <v>7085824</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,12 +1197,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2013-05-30</t>
+          <t>2021-06-06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2013-05-30</t>
+          <t>2021-06-06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1194,352 +1211,22 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AN6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>2 substratenheter # Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Magnus Johansson</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Johansson</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>74543225</v>
-      </c>
-      <c r="B7" t="n">
-        <v>91263</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Vikströms-Gravabergsmyran, Ång</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>695053</v>
-      </c>
-      <c r="R7" t="n">
-        <v>7086187</v>
-      </c>
-      <c r="S7" t="n">
-        <v>5</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Bjurholm</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Bjurholm</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2018-11-01</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2018-11-01</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Anna Hallmén</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Anna Hallmén</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>74543072</v>
-      </c>
-      <c r="B8" t="n">
-        <v>80083</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Vikströms-Gravabergsmyran, Ång</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>694532</v>
-      </c>
-      <c r="R8" t="n">
-        <v>7086592</v>
-      </c>
-      <c r="S8" t="n">
-        <v>5</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Bjurholm</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Bjurholm</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2018-11-01</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2018-11-01</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Anna Hallmén</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Anna Hallmén</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>17226080</v>
-      </c>
-      <c r="B9" t="n">
-        <v>91245</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Mellan Bjurvik och Norrnäs, Ång</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>694554</v>
-      </c>
-      <c r="R9" t="n">
-        <v>7086408</v>
-      </c>
-      <c r="S9" t="n">
-        <v>10</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Bjurholm</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Bjurholm</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2013-06-16</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2013-06-16</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AN9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>1 substratenheter # Picea abies</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Magnus Johansson</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Magnus Johansson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
